--- a/output/five-decade-tables/crowding_percent_by_group.xlsx
+++ b/output/five-decade-tables/crowding_percent_by_group.xlsx
@@ -653,22 +653,22 @@
         </is>
       </c>
       <c r="C14">
-        <v>10.66458729443639</v>
+        <v>19.68595664583058</v>
       </c>
       <c r="D14">
-        <v>6.838056961900254</v>
+        <v>11.56412506960371</v>
       </c>
       <c r="E14">
-        <v>8.247766684922107</v>
+        <v>12.81976515733746</v>
       </c>
       <c r="F14">
-        <v>10.21940536882986</v>
+        <v>14.40415035612742</v>
       </c>
       <c r="G14">
-        <v>5.609262085129805</v>
+        <v>8.683310229229663</v>
       </c>
       <c r="H14">
-        <v>5.257626187504263</v>
+        <v>7.279276740822678</v>
       </c>
     </row>
     <row r="15">
@@ -683,22 +683,22 @@
         </is>
       </c>
       <c r="C15">
-        <v>6.981782878431495</v>
+        <v>14.692699017289</v>
       </c>
       <c r="D15">
-        <v>3.260397411467037</v>
+        <v>7.919091004367634</v>
       </c>
       <c r="E15">
-        <v>3.153261927925294</v>
+        <v>8.507873851411807</v>
       </c>
       <c r="F15">
-        <v>3.638663719375171</v>
+        <v>11.09295128754513</v>
       </c>
       <c r="G15">
-        <v>1.755590834728596</v>
+        <v>6.109156794211463</v>
       </c>
       <c r="H15">
-        <v>2.245082406545349</v>
+        <v>6.251351291453436</v>
       </c>
     </row>
     <row r="16">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="C16">
-        <v>3.825162545678895</v>
+        <v>10.04035842493736</v>
       </c>
       <c r="D16">
-        <v>1.671791252919334</v>
+        <v>5.593952111016044</v>
       </c>
       <c r="E16">
-        <v>1.550024410353353</v>
+        <v>6.112116758140776</v>
       </c>
       <c r="F16">
-        <v>2.23562526333635</v>
+        <v>7.7121033346279</v>
       </c>
       <c r="G16">
-        <v>1.033373445955473</v>
+        <v>4.131937122736302</v>
       </c>
       <c r="H16">
-        <v>1.467309971027005</v>
+        <v>4.956771727322897</v>
       </c>
     </row>
     <row r="17">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="C17">
-        <v>2.347397163745266</v>
+        <v>7.722849979050141</v>
       </c>
       <c r="D17">
-        <v>1.214413696993828</v>
+        <v>4.756015291207556</v>
       </c>
       <c r="E17">
-        <v>1.06179937643241</v>
+        <v>4.753287717800117</v>
       </c>
       <c r="F17">
-        <v>1.666100373358352</v>
+        <v>5.724221943120704</v>
       </c>
       <c r="G17">
-        <v>0.6446839140196241</v>
+        <v>2.85951430563521</v>
       </c>
       <c r="H17">
-        <v>1.072956562966523</v>
+        <v>4.155617005558441</v>
       </c>
     </row>
     <row r="19">
